--- a/DB_Retail_Points_MAP.xlsx
+++ b/DB_Retail_Points_MAP.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,6 +491,31 @@
       </c>
       <c r="E3" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20:29:04</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ВкусВилл</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/DB_Retail_Points_MAP.xlsx
+++ b/DB_Retail_Points_MAP.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,6 +515,31 @@
         </is>
       </c>
       <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>14:09:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Твой Дом</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
       </c>
     </row>

--- a/DB_Retail_Points_MAP.xlsx
+++ b/DB_Retail_Points_MAP.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +543,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12:58:36</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ВкусВилл</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>17:08:05</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Алкотека</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DB_Retail_Points_MAP.xlsx
+++ b/DB_Retail_Points_MAP.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,6 +593,31 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>18:01:08</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SimpleWine</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DB_Retail_Points_MAP.xlsx
+++ b/DB_Retail_Points_MAP.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,6 +465,31 @@
         </is>
       </c>
       <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12:47:11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Озон</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
     </row>

--- a/DB_Retail_Points_MAP.xlsx
+++ b/DB_Retail_Points_MAP.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,6 +490,31 @@
         </is>
       </c>
       <c r="E3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>14:39:48</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Самокат</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
       </c>
     </row>

--- a/DB_Retail_Points_MAP.xlsx
+++ b/DB_Retail_Points_MAP.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,6 +515,31 @@
         </is>
       </c>
       <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11:42:57</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Утконос</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
       </c>
     </row>

--- a/DB_Retail_Points_MAP.xlsx
+++ b/DB_Retail_Points_MAP.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,6 +540,31 @@
         </is>
       </c>
       <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>11:56:07</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Вайлдберриз</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
     </row>

--- a/DB_Retail_Points_MAP.xlsx
+++ b/DB_Retail_Points_MAP.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -568,6 +568,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>11:28:43</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Гулливер</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11:43:14</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Гулливер</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ульяновск</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
